--- a/artfynd/A 49423-2025 artfynd.xlsx
+++ b/artfynd/A 49423-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>132183158</v>
       </c>
       <c r="B4" t="n">
-        <v>57780</v>
+        <v>57781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>132368144</v>
       </c>
       <c r="B5" t="n">
-        <v>57940</v>
+        <v>57941</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49423-2025 artfynd.xlsx
+++ b/artfynd/A 49423-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>132183158</v>
       </c>
       <c r="B4" t="n">
-        <v>57781</v>
+        <v>57785</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>132368144</v>
       </c>
       <c r="B5" t="n">
-        <v>57941</v>
+        <v>57945</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49423-2025 artfynd.xlsx
+++ b/artfynd/A 49423-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>87311481</v>
       </c>
       <c r="B2" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,12 +779,7 @@
         <v>119785943</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132183158</v>
+        <v>132368144</v>
       </c>
       <c r="B4" t="n">
-        <v>57786</v>
+        <v>57967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102622</v>
+        <v>100110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -924,7 +914,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -964,27 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Pisksnärtlätet flera gånger</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132368144</v>
+        <v>132183158</v>
       </c>
       <c r="B5" t="n">
-        <v>57949</v>
+        <v>57807</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100110</v>
+        <v>102622</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,7 +1023,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1088,12 +1063,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Pisksnärtlätet flera gånger</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,6 +1107,125 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133300944</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>N Flarkenvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>817944</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7313945</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lena Bondestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lena Bondestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
